--- a/artfynd/A 5712-2026 artfynd.xlsx
+++ b/artfynd/A 5712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133569220</v>
       </c>
       <c r="B2" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5712-2026 artfynd.xlsx
+++ b/artfynd/A 5712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133569220</v>
       </c>
       <c r="B2" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5712-2026 artfynd.xlsx
+++ b/artfynd/A 5712-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133569220</v>
+        <v>263668</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>96278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>756</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högmossen, Nybyn, Vstm</t>
+          <t>Blixbo (Kärr 600 m NNV om), Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554292</v>
+        <v>554396</v>
       </c>
       <c r="R2" t="n">
-        <v>6613952</v>
+        <v>6613856</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera högar med spillning. Inslag av spelspillning.</t>
+          <t>sparsamt / RikKärrsinventering, objektnr 11G3B321</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,23 +762,403 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
-      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Medelrikt källKärr, klass 2</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram rikkärr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>986307</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96543</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2682</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kärrkammossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Helodium blandowii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blixbo (Kärr 600 m NNV om), Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>554396</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6613856</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sparsamt / RikKärrsinventering, objektnr 11G3B321</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Medelrikt källKärr, klass 2</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram rikkärr</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133569220</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högmossen, Nybyn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>554292</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6613952</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera högar med spillning. Inslag av spelspillning.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Markus Nyberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Markus Nyberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>85138364</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58829</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vid forsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>554523</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6613958</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I rörelse nära Sämskarbobäcken</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>I skog mellan nybruten väg och mindre bäck. Marken täckt av grenar och mossa</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5712-2026 artfynd.xlsx
+++ b/artfynd/A 5712-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Åtgärdsprogram rikkärr</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/263668</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Åtgärdsprogram rikkärr</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/986307</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969344</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133569220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1287,8 +1312,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85138364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 5712-2026 artfynd.xlsx
+++ b/artfynd/A 5712-2026 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>134969344</v>
       </c>
       <c r="B4" t="n">
-        <v>57835</v>
+        <v>57840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
